--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{310D5463-35E8-4706-AE50-07F4D68A0E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3FF3D15-4BDF-4274-92D9-28E38D1D4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,7 +1248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0208D943-18E9-47F4-92D0-84750241B26B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8909A6-82C4-4750-ACED-D2CB2D989E9D}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1305,7 +1305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D64550-403E-474E-983B-2A20D20D1722}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCF0D5C-742D-4D60-B880-8E00D09E6B44}">
   <dimension ref="B9:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2007,7 +2007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738022F6-E037-460E-8FB5-84F988B35E49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB5C398-D8C2-4ABB-B3B0-A568C3ACDEC0}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3590,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20AB6BBC-56D7-4EA4-BFEF-E730C7A7046E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F068A7E-1315-44F8-8220-52428A29B63E}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3634,7 +3634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A60BA8-E79D-4578-8344-2A7919D2EAD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16026949-D82B-4ECD-9E69-0C911531A58A}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3683,7 +3683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614C753F-C090-4AF3-89EA-E69087D3FD8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F8D2DA0-A08D-4B6E-9ED2-EC4E4B390BDF}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3721,7 +3721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC68270-3B88-4125-B9C3-82776BEC52FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16267C32-3C20-4C64-B06E-3AF46E4475B5}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3837,7 +3837,7 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.2527166666666667</v>
+        <v>0.25271666666666665</v>
       </c>
       <c r="E17" t="s">
         <v>167</v>
@@ -3851,7 +3851,7 @@
         <v>37</v>
       </c>
       <c r="D18">
-        <v>0.28344999999999998</v>
+        <v>0.28345000000000004</v>
       </c>
       <c r="E18" t="s">
         <v>167</v>
@@ -3893,7 +3893,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.27348333333333336</v>
+        <v>0.2734833333333333</v>
       </c>
       <c r="E21" t="s">
         <v>167</v>
@@ -3963,7 +3963,7 @@
         <v>37</v>
       </c>
       <c r="D26">
-        <v>0.26475833333333337</v>
+        <v>0.26475833333333332</v>
       </c>
       <c r="E26" t="s">
         <v>167</v>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.26837499999999997</v>
+        <v>0.26837500000000003</v>
       </c>
       <c r="E32" t="s">
         <v>167</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.24309166666666668</v>
+        <v>0.24309166666666662</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D216862E-C86D-441B-B651-FD3A815D4CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15581820-436D-42D9-8ABC-8202FFA8E2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,7 +1248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D391BD-BBAC-414A-B0CE-C9500973FF0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D35546-1B1A-4F36-A72B-CB0777120AB6}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1305,7 +1305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175A1C3D-EF48-4250-81D8-929DD46B0F37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F95DEA53-AE7E-4E97-9CB0-85B9E75A64C3}">
   <dimension ref="B9:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2007,7 +2007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4247848-CFC6-411C-814D-9ACC46E45042}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9628EC3-4A27-4F9D-811C-40F7117C0B20}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3590,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807A3ECF-1498-4D57-90C2-599183F1F009}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6543E2-BDB7-4B84-853C-626F8F3DDAB7}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3634,7 +3634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCFCCD4-F7F0-4CB3-85C0-0EB8E2015F34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB2D468-53C1-4A69-9022-A3623A5CA8B5}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3683,7 +3683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E296A9C1-FC8F-4BF9-AE5D-34A3E36A22F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51937FEE-AAE8-4D11-B3A6-C38BC2C23B04}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3721,7 +3721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0962E5F7-FC80-4CC7-BC0C-FD1E62DD2EB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C65AA7B-F3C0-4DBE-B671-DB889555A3F3}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3823,7 +3823,7 @@
         <v>37</v>
       </c>
       <c r="D16">
-        <v>0.25275833333333336</v>
+        <v>0.25275833333333331</v>
       </c>
       <c r="E16" t="s">
         <v>167</v>
@@ -3879,7 +3879,7 @@
         <v>37</v>
       </c>
       <c r="D20">
-        <v>0.26399166666666668</v>
+        <v>0.26399166666666662</v>
       </c>
       <c r="E20" t="s">
         <v>167</v>
@@ -3893,7 +3893,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.27348333333333336</v>
+        <v>0.2734833333333333</v>
       </c>
       <c r="E21" t="s">
         <v>167</v>
@@ -3921,7 +3921,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.2649333333333333</v>
+        <v>0.26493333333333335</v>
       </c>
       <c r="E23" t="s">
         <v>167</v>
@@ -3935,7 +3935,7 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.25725833333333337</v>
+        <v>0.25725833333333331</v>
       </c>
       <c r="E24" t="s">
         <v>167</v>
@@ -3963,7 +3963,7 @@
         <v>37</v>
       </c>
       <c r="D26">
-        <v>0.26475833333333337</v>
+        <v>0.26475833333333332</v>
       </c>
       <c r="E26" t="s">
         <v>167</v>
@@ -3977,7 +3977,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.28628333333333328</v>
+        <v>0.28628333333333339</v>
       </c>
       <c r="E27" t="s">
         <v>167</v>
@@ -4005,7 +4005,7 @@
         <v>37</v>
       </c>
       <c r="D29">
-        <v>0.27752500000000002</v>
+        <v>0.27752499999999997</v>
       </c>
       <c r="E29" t="s">
         <v>167</v>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.26837500000000003</v>
+        <v>0.26837499999999997</v>
       </c>
       <c r="E32" t="s">
         <v>167</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.24309166666666662</v>
+        <v>0.24309166666666668</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>
@@ -4117,7 +4117,7 @@
         <v>37</v>
       </c>
       <c r="D37">
-        <v>0.26184166666666669</v>
+        <v>0.26184166666666664</v>
       </c>
       <c r="E37" t="s">
         <v>167</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9479C3C-4BAE-4A63-8FAB-ECDF4B726F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6A888F3-765B-40FE-97A1-F874552A9A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -809,7 +809,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{845C4823-024C-14C7-9FAA-F3F2B28E246A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEBEADF2-44D3-DFB5-640A-FFD69094C17C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -864,7 +864,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7D8BA1D-AD58-84EC-1FEF-516E645305C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{641256EA-EE3D-14EB-7872-ABF1BA71CDDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -919,7 +919,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{106D8E5A-C0E1-DA98-CB6E-B27CEC48B3BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1CEB765-1FB7-15CC-9F18-CCB009F6EAE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -974,7 +974,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F50909E5-F98A-E081-F9BE-9BF2B2013D73}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{620E0B4D-DD51-DC53-EB20-A62B03CF95FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1029,7 +1029,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25AB7543-C33B-1CEE-D6E7-7726504FBFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB0B47B3-5F1F-EF03-5808-FF3FF4E3FBB1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1084,7 +1084,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2516CB31-F355-959E-050D-0CCAB1FC30E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0CD9EA1-6B17-687F-DBCF-F533D2560AFF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1139,7 +1139,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C2813B4-1F00-AD71-29CA-39577EDD9813}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECA0C7B7-6233-C9E0-D363-0E19A93310F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1194,7 +1194,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4C00586-9812-3CC6-0B8E-62539B35629B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89E5357A-1717-6A81-6667-01FF5F83E657}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1809,7 +1809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34E88F5-EE5F-41A8-83F1-E8134A2CF5C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BA48B36-36FC-4BA9-A784-3A179F483FA4}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1885,7 +1885,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4132C1-2623-47C3-BAE3-AC5ABF7023C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261C68EE-E0C6-4238-90E4-E00871548AFA}">
   <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2611,7 +2611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC734052-A75E-4202-BEC9-DD5B40D468D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D95ECF-F70B-4358-BAFF-5D9987BEAC71}">
   <dimension ref="A1:T60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4227,7 +4227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB419227-D675-44F1-AF01-D52F44681811}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9B6707-544E-4A90-A34D-3E5D378F495C}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4291,7 +4291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604A1A28-A6C1-4183-99C3-DE3526C7F878}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F8F73A-4592-4591-B195-9033D370441D}">
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4360,7 +4360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869B039F-2116-4A3F-BF68-27E2187015BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A8ED65-5D11-481F-9B7E-B41FB5841401}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4418,7 +4418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D18001A-4E06-40A6-B258-B65E64139D64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A8E426-2102-4C33-9E4E-3E64237873B5}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4465,7 +4465,7 @@
         <v>37</v>
       </c>
       <c r="D11" s="19">
-        <v>0.18843333333333334</v>
+        <v>0.18843333333333331</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>168</v>
@@ -4479,7 +4479,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="22">
-        <v>0.21560000000000001</v>
+        <v>0.21559999999999999</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>168</v>
@@ -4535,7 +4535,7 @@
         <v>37</v>
       </c>
       <c r="D16" s="22">
-        <v>0.25275833333333336</v>
+        <v>0.25275833333333331</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>168</v>
@@ -4563,7 +4563,7 @@
         <v>37</v>
       </c>
       <c r="D18" s="22">
-        <v>0.28344999999999998</v>
+        <v>0.28345000000000004</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>168</v>
@@ -4577,7 +4577,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="19">
-        <v>0.27329166666666665</v>
+        <v>0.27329166666666671</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>168</v>
@@ -4619,7 +4619,7 @@
         <v>37</v>
       </c>
       <c r="D22" s="22">
-        <v>0.26017499999999999</v>
+        <v>0.26017500000000005</v>
       </c>
       <c r="E22" s="21" t="s">
         <v>168</v>
@@ -4675,7 +4675,7 @@
         <v>37</v>
       </c>
       <c r="D26" s="22">
-        <v>0.26475833333333332</v>
+        <v>0.26475833333333337</v>
       </c>
       <c r="E26" s="21" t="s">
         <v>168</v>
@@ -4689,7 +4689,7 @@
         <v>37</v>
       </c>
       <c r="D27" s="19">
-        <v>0.28628333333333328</v>
+        <v>0.28628333333333339</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>168</v>
@@ -4717,7 +4717,7 @@
         <v>37</v>
       </c>
       <c r="D29" s="19">
-        <v>0.27752499999999997</v>
+        <v>0.27752500000000002</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>168</v>
@@ -4759,7 +4759,7 @@
         <v>37</v>
       </c>
       <c r="D32" s="22">
-        <v>0.26837499999999997</v>
+        <v>0.26837500000000003</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>168</v>
@@ -4773,7 +4773,7 @@
         <v>37</v>
       </c>
       <c r="D33" s="19">
-        <v>0.24309166666666668</v>
+        <v>0.24309166666666671</v>
       </c>
       <c r="E33" s="18" t="s">
         <v>168</v>
@@ -4829,7 +4829,7 @@
         <v>37</v>
       </c>
       <c r="D37" s="19">
-        <v>0.26184166666666664</v>
+        <v>0.26184166666666669</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>168</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC6B73EA-B0BA-449F-8ECC-E060BCB7DF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67945D91-33E7-4844-A575-7A6CA95E5450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,7 +1248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FFD574-E826-47CD-85F6-495E5D650CED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B67C64-5881-44FF-9B1A-AD95B5958273}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1305,7 +1305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4E6BF0-3682-49B6-B538-AB56C111E13B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64353813-9375-49E6-ADB3-7D0F7815947C}">
   <dimension ref="B9:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2007,7 +2007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E60A41-D1CD-433B-B150-4BA2998063BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC66947-D140-4E1F-B9B9-3FD2C843AD71}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3590,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEAEC33-027B-41AC-8110-B5CE5745B2F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A0354BC-D427-47EE-B60E-9AE4E19638DB}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3634,7 +3634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D441EE-296D-4B41-A6F2-C806EC81B22B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8273421-F07E-4E80-8AFF-0A796D13FDDD}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3683,7 +3683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B7D917-56CF-4564-87D9-E6EF7D58C4F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11E18EA-5A6A-4B57-878E-1E9C4C4C8245}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3721,7 +3721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB881AB4-E050-4365-9FE8-EEF03B6B13CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B5440D1-7445-4450-906F-5D7991BF5BC2}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3753,7 +3753,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.18843333333333331</v>
+        <v>0.18843333333333334</v>
       </c>
       <c r="E11" t="s">
         <v>167</v>
@@ -3767,7 +3767,7 @@
         <v>37</v>
       </c>
       <c r="D12">
-        <v>0.21559999999999999</v>
+        <v>0.21560000000000001</v>
       </c>
       <c r="E12" t="s">
         <v>167</v>
@@ -3893,7 +3893,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.27348333333333336</v>
+        <v>0.2734833333333333</v>
       </c>
       <c r="E21" t="s">
         <v>167</v>
@@ -3921,7 +3921,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.26493333333333335</v>
+        <v>0.26493333333333341</v>
       </c>
       <c r="E23" t="s">
         <v>167</v>
@@ -3963,7 +3963,7 @@
         <v>37</v>
       </c>
       <c r="D26">
-        <v>0.26475833333333337</v>
+        <v>0.26475833333333332</v>
       </c>
       <c r="E26" t="s">
         <v>167</v>
@@ -4005,7 +4005,7 @@
         <v>37</v>
       </c>
       <c r="D29">
-        <v>0.27752500000000002</v>
+        <v>0.27752499999999997</v>
       </c>
       <c r="E29" t="s">
         <v>167</v>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.26837500000000003</v>
+        <v>0.26837499999999997</v>
       </c>
       <c r="E32" t="s">
         <v>167</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.24309166666666668</v>
+        <v>0.24309166666666671</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>
@@ -4117,7 +4117,7 @@
         <v>37</v>
       </c>
       <c r="D37">
-        <v>0.26184166666666669</v>
+        <v>0.26184166666666664</v>
       </c>
       <c r="E37" t="s">
         <v>167</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67945D91-33E7-4844-A575-7A6CA95E5450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ED53D7A-8B8B-4B7A-B331-DDD7A13CA4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,7 +1248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B67C64-5881-44FF-9B1A-AD95B5958273}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA7390F4-E5A5-47CA-B6F4-6963866B7042}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1305,7 +1305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64353813-9375-49E6-ADB3-7D0F7815947C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC0958-A3FE-4D28-95FF-EAF1597AA9EC}">
   <dimension ref="B9:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2007,7 +2007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC66947-D140-4E1F-B9B9-3FD2C843AD71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF5057F-A304-4C17-B2CB-FA2965B52B16}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3590,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A0354BC-D427-47EE-B60E-9AE4E19638DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0960877F-BE96-46D4-B9ED-0D036E224E6F}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3634,7 +3634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8273421-F07E-4E80-8AFF-0A796D13FDDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BBB3D7-DD49-4458-A486-45520506973A}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3683,7 +3683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11E18EA-5A6A-4B57-878E-1E9C4C4C8245}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88018AB-EE10-444A-8DDE-39CB480AF506}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3721,7 +3721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B5440D1-7445-4450-906F-5D7991BF5BC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBB1818-86F6-4A8F-9C84-771089E62740}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3823,7 +3823,7 @@
         <v>37</v>
       </c>
       <c r="D16">
-        <v>0.25275833333333336</v>
+        <v>0.25275833333333331</v>
       </c>
       <c r="E16" t="s">
         <v>167</v>
@@ -3837,7 +3837,7 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.2527166666666667</v>
+        <v>0.25271666666666665</v>
       </c>
       <c r="E17" t="s">
         <v>167</v>
@@ -3851,7 +3851,7 @@
         <v>37</v>
       </c>
       <c r="D18">
-        <v>0.28344999999999998</v>
+        <v>0.28345000000000004</v>
       </c>
       <c r="E18" t="s">
         <v>167</v>
@@ -4005,7 +4005,7 @@
         <v>37</v>
       </c>
       <c r="D29">
-        <v>0.27752499999999997</v>
+        <v>0.27752500000000002</v>
       </c>
       <c r="E29" t="s">
         <v>167</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.24309166666666671</v>
+        <v>0.24309166666666668</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ED53D7A-8B8B-4B7A-B331-DDD7A13CA4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1D91725-1097-4FC8-A4B1-B041C6A3D25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,7 +1248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA7390F4-E5A5-47CA-B6F4-6963866B7042}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E7399A1-7726-4A59-9E71-99870CFEC837}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1305,7 +1305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC0958-A3FE-4D28-95FF-EAF1597AA9EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4D2D57-BFEB-4B8F-AF41-2D9E72F74840}">
   <dimension ref="B9:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2007,7 +2007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF5057F-A304-4C17-B2CB-FA2965B52B16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3481AAFB-8B0C-416F-B9AF-E574A89D725F}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3590,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0960877F-BE96-46D4-B9ED-0D036E224E6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14ED70-6DF8-4267-BFC0-E43A936201D3}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3634,7 +3634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BBB3D7-DD49-4458-A486-45520506973A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC12B631-BBAC-45C3-AEC0-58A3AA7E609D}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3683,7 +3683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88018AB-EE10-444A-8DDE-39CB480AF506}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EFAAC2E-27FD-4034-9234-2BA0A522A82C}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3721,7 +3721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBB1818-86F6-4A8F-9C84-771089E62740}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD6FBEE-0B75-4081-B8CC-3A30504DE04F}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3781,7 +3781,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.18140833333333331</v>
+        <v>0.18140833333333337</v>
       </c>
       <c r="E13" t="s">
         <v>167</v>
@@ -3837,7 +3837,7 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.25271666666666665</v>
+        <v>0.2527166666666667</v>
       </c>
       <c r="E17" t="s">
         <v>167</v>
@@ -3851,7 +3851,7 @@
         <v>37</v>
       </c>
       <c r="D18">
-        <v>0.28345000000000004</v>
+        <v>0.28344999999999998</v>
       </c>
       <c r="E18" t="s">
         <v>167</v>
@@ -3893,7 +3893,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.2734833333333333</v>
+        <v>0.27348333333333336</v>
       </c>
       <c r="E21" t="s">
         <v>167</v>
@@ -3921,7 +3921,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.26493333333333341</v>
+        <v>0.26493333333333335</v>
       </c>
       <c r="E23" t="s">
         <v>167</v>
@@ -3977,7 +3977,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.28628333333333333</v>
+        <v>0.28628333333333328</v>
       </c>
       <c r="E27" t="s">
         <v>167</v>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.26837499999999997</v>
+        <v>0.26837500000000003</v>
       </c>
       <c r="E32" t="s">
         <v>167</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.24309166666666668</v>
+        <v>0.24309166666666662</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>
@@ -4117,7 +4117,7 @@
         <v>37</v>
       </c>
       <c r="D37">
-        <v>0.26184166666666664</v>
+        <v>0.26184166666666669</v>
       </c>
       <c r="E37" t="s">
         <v>167</v>
